--- a/examples/HFP_chris+pat.xlsx
+++ b/examples/HFP_chris+pat.xlsx
@@ -508,85 +508,85 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
+      <c r="B2" t="n">
+        <v>160000</v>
+      </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="F2" t="n">
+        <v>26000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2022</v>
       </c>
+      <c r="B3" t="n">
+        <v>165000</v>
+      </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
+      <c r="F3" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>2023</v>
       </c>
+      <c r="B4" t="n">
+        <v>170000</v>
+      </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
+      <c r="F4" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>2024</v>
       </c>
+      <c r="B5" t="n">
+        <v>155000</v>
+      </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
+      <c r="F5" t="n">
+        <v>30500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>2025</v>
       </c>
+      <c r="B6" t="n">
+        <v>130000</v>
+      </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
+      <c r="F6" t="n">
+        <v>31000</v>
       </c>
     </row>
     <row r="7">
@@ -603,10 +603,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>23000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
+        <v>29300</v>
       </c>
     </row>
     <row r="8">
@@ -614,7 +611,7 @@
         <v>2027</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -623,26 +620,17 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
+        <v>29300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>2028</v>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -656,9 +644,6 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -670,9 +655,6 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -684,9 +666,6 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -698,9 +677,6 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -712,9 +688,6 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -726,9 +699,6 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -740,9 +710,6 @@
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -754,9 +721,6 @@
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -768,9 +732,6 @@
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -782,9 +743,6 @@
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -796,9 +754,6 @@
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -810,9 +765,6 @@
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -824,9 +776,6 @@
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -838,9 +787,6 @@
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -852,9 +798,6 @@
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -866,9 +809,6 @@
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -880,9 +820,6 @@
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -894,9 +831,6 @@
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -908,9 +842,6 @@
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -922,9 +853,6 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -936,9 +864,6 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -950,9 +875,6 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -964,9 +886,6 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -978,9 +897,6 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -992,9 +908,6 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1006,9 +919,6 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1018,9 +928,6 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1104,85 +1011,85 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
+      <c r="B2" t="n">
+        <v>68000</v>
+      </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="F2" t="n">
+        <v>26000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2022</v>
       </c>
+      <c r="B3" t="n">
+        <v>72000</v>
+      </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
+      <c r="F3" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>2023</v>
       </c>
+      <c r="B4" t="n">
+        <v>75000</v>
+      </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
+      <c r="F4" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>2024</v>
       </c>
+      <c r="B5" t="n">
+        <v>78000</v>
+      </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12000</v>
+      <c r="F5" t="n">
+        <v>30500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>2025</v>
       </c>
+      <c r="B6" t="n">
+        <v>80000</v>
+      </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
+      <c r="F6" t="n">
+        <v>31000</v>
       </c>
     </row>
     <row r="7">
@@ -1199,10 +1106,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>23000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4000</v>
+        <v>27700</v>
       </c>
     </row>
     <row r="8">
@@ -1219,10 +1123,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>23000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4000</v>
+        <v>27700</v>
       </c>
     </row>
     <row r="9">
@@ -1239,10 +1140,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>23000</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4000</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="10">
@@ -1255,9 +1153,6 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="n">
-        <v>4000</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1269,9 +1164,6 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="n">
-        <v>4000</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1283,9 +1175,6 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1297,9 +1186,6 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1311,9 +1197,6 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1325,9 +1208,6 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1339,9 +1219,6 @@
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1353,9 +1230,6 @@
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1367,9 +1241,6 @@
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1381,9 +1252,6 @@
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1395,9 +1263,6 @@
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1409,9 +1274,6 @@
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1423,9 +1285,6 @@
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1437,9 +1296,6 @@
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1451,9 +1307,6 @@
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1465,9 +1318,6 @@
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1479,9 +1329,6 @@
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1493,9 +1340,6 @@
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1507,9 +1351,6 @@
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1521,9 +1362,6 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1535,9 +1373,6 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1549,9 +1384,6 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1563,9 +1395,6 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1577,9 +1406,6 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1591,9 +1417,6 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1605,9 +1428,6 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1619,9 +1439,6 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1633,9 +1450,6 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1647,9 +1461,6 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1659,9 +1470,6 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
         <v>0</v>
       </c>
     </row>

--- a/examples/HFP_chris+pat.xlsx
+++ b/examples/HFP_chris+pat.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Chris" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pat" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Debts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Fixed Assets" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chris" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pat" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1609,7 +1609,7 @@
         <v>450000</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>

--- a/examples/HFP_chris+pat.xlsx
+++ b/examples/HFP_chris+pat.xlsx
@@ -1,37 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chris" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pat" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Chris" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pat" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Debts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fixed Assets" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,33 +45,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -439,66 +416,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:M36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>anticipated wages</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -517,9 +499,19 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>26000</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -534,9 +526,19 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>27000</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -551,9 +553,19 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>30000</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -568,9 +580,19 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>30500</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -585,9 +607,19 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>31000</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -602,9 +634,19 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>29300</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -619,317 +661,663 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>29300</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>2028</v>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>2029</v>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>2030</v>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>2031</v>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>2032</v>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>2033</v>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>2034</v>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>2035</v>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>2036</v>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>2037</v>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>2038</v>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>2039</v>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>2040</v>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>2041</v>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>2042</v>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>2043</v>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>2044</v>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>2045</v>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>2046</v>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>2047</v>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>2048</v>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>2049</v>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>2050</v>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>2051</v>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>2052</v>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>2053</v>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>2054</v>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>2055</v>
       </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -942,66 +1330,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:M39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>anticipated wages</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -1020,9 +1413,19 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>26000</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1037,9 +1440,19 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>27000</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1054,9 +1467,19 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>30000</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,9 +1494,19 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>30500</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1088,9 +1521,19 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>31000</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1105,9 +1548,19 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>27700</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1122,9 +1575,19 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>27700</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1139,339 +1602,709 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>27900</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>2029</v>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>2030</v>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>2031</v>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>2032</v>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>2033</v>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>2034</v>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>2035</v>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>2036</v>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>2037</v>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>2038</v>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>2039</v>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>2040</v>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>2041</v>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>2042</v>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>2043</v>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>2044</v>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>2045</v>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>2046</v>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>2047</v>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>2048</v>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>2049</v>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>2050</v>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>2051</v>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>2052</v>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>2053</v>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>2054</v>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>2055</v>
       </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>2056</v>
       </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>2057</v>
       </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>2058</v>
       </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1485,40 +2318,40 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>term</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
@@ -1536,50 +2369,50 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>yod</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>commission</t>
         </is>

--- a/examples/HFP_chris+pat.xlsx
+++ b/examples/HFP_chris+pat.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,10 +477,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -499,19 +504,12 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>26000</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -526,19 +524,12 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>27000</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -553,19 +544,12 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>30000</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -580,19 +564,12 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>30500</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -607,19 +584,12 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>31000</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -634,19 +604,12 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>29300</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -661,663 +624,404 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>29300</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>2028</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1330,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1391,10 +1095,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -1413,19 +1122,12 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>26000</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1440,19 +1142,12 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>27000</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1467,19 +1162,12 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>30000</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1494,19 +1182,12 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>30500</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1521,19 +1202,12 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>31000</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1548,19 +1222,12 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>27700</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1575,19 +1242,12 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>27700</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1602,709 +1262,432 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>27900</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>2056</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>2057</v>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>2058</v>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
